--- a/examples/qualibact_ecoli/pass_only/report/report.xlsx
+++ b/examples/qualibact_ecoli/pass_only/report/report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,82 +489,112 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Checkm.Total_Coding_Sequences</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>Checkm.all_checks_passed</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Quast.# contigs (&gt;= 0 bp)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Quast.GC (%)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Quast.Largest contig</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Quast.N50</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Quast.Total length</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Quast.Total length (&gt;= 0 bp)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Quast.all_checks_passed</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Speciator.all_checks_passed</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Speciator.confidence</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Speciator.speciesName</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Sylph.all_checks_passed</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Sylph.number_of_genomes</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Sylph.top_species</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Sylph.top_taxonomic_abundance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>all_checks_passed</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_tier</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_passed</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_reasons</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_warn_policy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_source</t>
         </is>
       </c>
     </row>
@@ -574,23 +604,35 @@
           <t>SAMN42766885</t>
         </is>
       </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>184</v>
@@ -610,59 +652,97 @@
       <c r="M2" t="n">
         <v>120461</v>
       </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="N2" t="n">
+        <v>4844</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>184</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>50.4198</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>684542</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>120461</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5043262</v>
       </c>
       <c r="T2" t="n">
         <v>5043262</v>
       </c>
-      <c r="U2" t="b">
+      <c r="U2" t="n">
+        <v>5043262</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
         <v>1</v>
       </c>
-      <c r="V2" t="b">
-        <v>1</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Escherichia coli</t>
         </is>
       </c>
-      <c r="Y2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AC2" t="b">
-        <v>1</v>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>warn-as-warn</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -671,23 +751,35 @@
           <t>SAMN42766886</t>
         </is>
       </c>
-      <c r="B3" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="H3" t="n">
         <v>159</v>
@@ -707,59 +799,97 @@
       <c r="M3" t="n">
         <v>172285</v>
       </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="N3" t="n">
+        <v>5050</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>159</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>50.6951</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>578018</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>172285</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5269811</v>
       </c>
       <c r="T3" t="n">
         <v>5269811</v>
       </c>
-      <c r="U3" t="b">
+      <c r="U3" t="n">
+        <v>5269811</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
         <v>1</v>
       </c>
-      <c r="V3" t="b">
-        <v>1</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Escherichia coli</t>
         </is>
       </c>
-      <c r="Y3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>0.95</v>
       </c>
-      <c r="AC3" t="b">
-        <v>1</v>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>warn-as-warn</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -898,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,12 +1113,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sylph.top_species</t>
+          <t>qualibact_compat_tier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1004,25 +1134,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sylph.top_taxonomic_abundance</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+          <t>Sylph.top_species</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sylph.top_taxonomic_abundance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>

--- a/examples/qualibact_ecoli/pass_only/report/report.xlsx
+++ b/examples/qualibact_ecoli/pass_only/report/report.xlsx
@@ -7,12 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="qc_status" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Species assignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Assembly quality" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Completeness and contamination" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Coverage and abundance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="full" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="qc_status" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Species assignment" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assembly quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Completeness and contamination" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Coverage and abundance" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,172 +431,72 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Checkm.Completeness.check</t>
+          <t>overall_qc</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Checkm.Contamination.check</t>
+          <t>all_checks_passed</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Quast.# contigs (&gt;= 0 bp).check</t>
+          <t>qualibact_compat_tier</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Quast.GC (%).check</t>
+          <t>species</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Quast.N50.check</t>
+          <t>species_confidence</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Quast.Total length (&gt;= 0 bp).check</t>
+          <t>n50</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Checkm.# contigs</t>
+          <t>contigs</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Checkm.Completeness</t>
+          <t>genome_size</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Checkm.Contamination</t>
+          <t>gc_percent</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Checkm.GC</t>
+          <t>completeness</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Checkm.Genome size (bp)</t>
+          <t>contamination</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Checkm.N50 (scaffolds)</t>
+          <t>top_species</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Checkm.Total_Coding_Sequences</t>
+          <t>top_abundance</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Checkm.all_checks_passed</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Quast.# contigs (&gt;= 0 bp)</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Quast.GC (%)</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Quast.Largest contig</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Quast.N50</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Quast.Total length</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Quast.Total length (&gt;= 0 bp)</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Quast.all_checks_passed</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Speciator.all_checks_passed</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Speciator.confidence</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Speciator.speciesName</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Sylph.all_checks_passed</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Sylph.number_of_genomes</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Sylph.top_species</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Sylph.top_taxonomic_abundance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>all_checks_passed</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>qualibact_compat_tier</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>qualibact_compat_passed</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>qualibact_compat_reasons</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>qualibact_compat_warn_policy</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>qualibact_compat_source</t>
+          <t>reason_summary</t>
         </is>
       </c>
     </row>
@@ -606,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -616,132 +518,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>120461</v>
       </c>
       <c r="H2" t="n">
         <v>184</v>
       </c>
       <c r="I2" t="n">
+        <v>5043262</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50.4198</v>
+      </c>
+      <c r="K2" t="n">
         <v>100</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.21</v>
       </c>
-      <c r="K2" t="n">
-        <v>50.4198</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5043262</v>
-      </c>
-      <c r="M2" t="n">
-        <v>120461</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
       </c>
       <c r="N2" t="n">
-        <v>4844</v>
+        <v>0.95</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>184</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>50.4198</v>
-      </c>
-      <c r="R2" t="n">
-        <v>684542</v>
-      </c>
-      <c r="S2" t="n">
-        <v>120461</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5043262</v>
-      </c>
-      <c r="U2" t="n">
-        <v>5043262</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
           <t>none</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>warn-as-warn</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
         </is>
       </c>
     </row>
@@ -753,7 +571,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,132 +581,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>172285</v>
       </c>
       <c r="H3" t="n">
         <v>159</v>
       </c>
       <c r="I3" t="n">
+        <v>5269811</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50.6951</v>
+      </c>
+      <c r="K3" t="n">
         <v>100</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K3" t="n">
-        <v>50.6951</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5269811</v>
-      </c>
-      <c r="M3" t="n">
-        <v>172285</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>5050</v>
+        <v>0.95</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>50.6951</v>
-      </c>
-      <c r="R3" t="n">
-        <v>578018</v>
-      </c>
-      <c r="S3" t="n">
-        <v>172285</v>
-      </c>
-      <c r="T3" t="n">
-        <v>5269811</v>
-      </c>
-      <c r="U3" t="n">
-        <v>5269811</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
           <t>none</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>warn-as-warn</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
         </is>
       </c>
     </row>
@@ -903,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,32 +648,72 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Checkm</t>
+          <t>overall_qc</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Quast</t>
+          <t>all_checks_passed</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Speciator</t>
+          <t>qualibact_compat_tier</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Sylph</t>
+          <t>species</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>all_checks_passed</t>
+          <t>species_confidence</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>QC_PASS</t>
+          <t>n50</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>contigs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>genome_size</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gc_percent</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>contamination</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>top_species</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>top_abundance</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason_summary</t>
         </is>
       </c>
     </row>
@@ -951,7 +725,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -961,22 +735,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>120461</v>
+      </c>
+      <c r="H2" t="n">
+        <v>184</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5043262</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50.4198</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -988,7 +788,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -998,22 +798,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>172285</v>
+      </c>
+      <c r="H3" t="n">
+        <v>159</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5269811</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50.6951</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -1028,154 +854,559 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:AO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Most common</t>
+          <t>Checkm.Completeness.check</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unique values</t>
+          <t>Checkm.Contamination.check</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Quast.# contigs (&gt;= 0 bp).check</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Quast.GC (%).check</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>Quast.N50.check</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Quast.Total length (&gt;= 0 bp).check</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Checkm.# contigs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Checkm.Completeness</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Checkm.Contamination</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Checkm.GC</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Checkm.Genome size (bp)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Checkm.N50 (scaffolds)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Checkm.Total_Coding_Sequences</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Checkm.all_checks_passed</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Quast.# contigs (&gt;= 0 bp)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Quast.GC (%)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Quast.Largest contig</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Quast.N50</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Quast.Total length</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Quast.Total length (&gt;= 0 bp)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Quast.all_checks_passed</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Speciator.all_checks_passed</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Speciator.confidence</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Speciator.speciesName</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Sylph.all_checks_passed</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Sylph.number_of_genomes</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Sylph.top_species</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Sylph.top_taxonomic_abundance</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>all_checks_passed</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_tier</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_passed</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_reasons</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_warn_policy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_source</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_metrics_evaluated</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_metrics_missing</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>overall_qc</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>species</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>species_confidence</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>reason_summary</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Speciator.speciesName</t>
+          <t>SAMN42766885</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>184</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K2" t="n">
+        <v>50.4198</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5043262</v>
+      </c>
+      <c r="M2" t="n">
+        <v>120461</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4844</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>184</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>50.4198</v>
+      </c>
+      <c r="R2" t="n">
+        <v>684542</v>
+      </c>
+      <c r="S2" t="n">
+        <v>120461</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5043262</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5043262</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>Escherichia coli</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>warn-as-warn</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Speciator.confidence</t>
+          <t>SAMN42766886</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>159</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50.6951</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5269811</v>
+      </c>
+      <c r="M3" t="n">
+        <v>172285</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5050</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>50.6951</v>
+      </c>
+      <c r="R3" t="n">
+        <v>578018</v>
+      </c>
+      <c r="S3" t="n">
+        <v>172285</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5269811</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5269811</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>good</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>warn-as-warn</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>qualibact_compat_tier</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sylph.top_species</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>Escherichia coli</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sylph.top_taxonomic_abundance</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.95</t>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -1190,159 +1421,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>sample_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Checkm</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>Quast</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Speciator</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Sylph</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>all_checks_passed</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>QC_PASS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Quast.N50</t>
+          <t>SAMN42766885</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>120,461</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>146,373</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>172,285</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quast.# contigs (&gt;= 0 bp)</t>
+          <t>SAMN42766886</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>171.50</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Quast.Total length</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5,043,262</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5,156,536.50</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5,269,811</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Quast.GC (%)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>50.42</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>50.70</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Quast.Largest contig</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>578,018</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>631,280</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>684,542</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1356,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,123 +1557,144 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Most common</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unique values</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Max</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Missing</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Checkm.Completeness</t>
+          <t>Speciator.speciesName</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Checkm.Contamination</t>
+          <t>Speciator.confidence</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Checkm.GC</t>
+          <t>qualibact_compat_tier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>50.42</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>50.70</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Checkm.Genome size (bp)</t>
+          <t>Sylph.top_species</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5,043,262</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5,156,536.50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5,269,811</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sylph.top_taxonomic_abundance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1497,6 +1708,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Quast.N50</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>120,461</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>146,373</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>172,285</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Quast.# contigs (&gt;= 0 bp)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>171.50</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Quast.Total length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5,043,262</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5,156,536.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5,269,811</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Quast.GC (%)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50.42</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>50.56</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50.70</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Quast.Largest contig</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>578,018</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>631,280</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>684,542</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Checkm.Completeness</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Checkm.Contamination</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Checkm.GC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>50.42</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>50.56</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>50.70</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Checkm.Genome size (bp)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5,043,262</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5,156,536.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5,269,811</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
